--- a/bin/rfc_agencies_source.xlsx
+++ b/bin/rfc_agencies_source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa-github\bin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846E264C-14AF-4677-8226-D8FB078E1D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D71586-0E36-4664-9739-CA2A196050A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Access Board</t>
   </si>
@@ -202,13 +202,19 @@
   </si>
   <si>
     <t>NEA</t>
+  </si>
+  <si>
+    <t>FY24</t>
+  </si>
+  <si>
+    <t>SEC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +240,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -553,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB35"/>
+  <dimension ref="A1:AB36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -641,6 +653,9 @@
       <c r="V1" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="W1" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -746,6 +761,9 @@
       <c r="V3" s="5">
         <v>1</v>
       </c>
+      <c r="W3" s="5">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -769,6 +787,9 @@
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -828,6 +849,9 @@
       <c r="V6" s="5">
         <v>3</v>
       </c>
+      <c r="W6" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -894,6 +918,9 @@
         <v>2</v>
       </c>
       <c r="V7" s="5">
+        <v>1</v>
+      </c>
+      <c r="W7" s="5">
         <v>1</v>
       </c>
     </row>
@@ -1183,8 +1210,11 @@
       <c r="V16" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1195,7 +1225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1231,14 +1261,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1252,7 +1282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1275,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -1284,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1304,7 +1334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1330,7 +1360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -1356,8 +1386,11 @@
       <c r="V26" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>42</v>
       </c>
@@ -1365,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -1373,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -1381,7 +1414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1404,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>49</v>
       </c>
@@ -1421,7 +1454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -1429,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -1443,7 +1476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -1451,7 +1484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -1462,7 +1495,16 @@
         <v>2</v>
       </c>
     </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/bin/rfc_agencies_source.xlsx
+++ b/bin/rfc_agencies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\IQA\iqa\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D71586-0E36-4664-9739-CA2A196050A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB76C8-DC83-497B-AACC-EBCF2178D3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Access Board</t>
   </si>
@@ -208,6 +211,9 @@
   </si>
   <si>
     <t>SEC</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -656,6 +662,9 @@
       <c r="W1" s="5" t="s">
         <v>56</v>
       </c>
+      <c r="X1" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -852,6 +861,9 @@
       <c r="W6" s="5">
         <v>1</v>
       </c>
+      <c r="X6" s="5">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -923,6 +935,9 @@
       <c r="W7" s="5">
         <v>1</v>
       </c>
+      <c r="X7" s="5">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -991,7 +1006,9 @@
       <c r="V8" s="7">
         <v>1</v>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3">
+        <v>4</v>
+      </c>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
@@ -1068,6 +1085,9 @@
       <c r="P11">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1093,6 +1113,12 @@
       <c r="V12" s="5">
         <v>9</v>
       </c>
+      <c r="W12" s="5">
+        <v>4</v>
+      </c>
+      <c r="X12" s="5">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1212,6 +1238,9 @@
       </c>
       <c r="W16" s="5">
         <v>3</v>
+      </c>
+      <c r="X16" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
